--- a/portfolio/posts/_data/TRUCK_RECORDS.xlsx
+++ b/portfolio/posts/_data/TRUCK_RECORDS.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1889" uniqueCount="173">
   <si>
     <t>Data checked through 2019</t>
   </si>
@@ -509,6 +509,39 @@
   </si>
   <si>
     <t>AC to Lonewolf</t>
+  </si>
+  <si>
+    <t>Chippewa Costco</t>
+  </si>
+  <si>
+    <t>CR KwikTrip</t>
+  </si>
+  <si>
+    <t>Drummond</t>
+  </si>
+  <si>
+    <t>AC to Washburn &amp; Superior</t>
+  </si>
+  <si>
+    <t>Poplar Shell</t>
+  </si>
+  <si>
+    <t>AC to Superior</t>
+  </si>
+  <si>
+    <t>AC to Superior (2x)</t>
+  </si>
+  <si>
+    <t>AC to Superior (2.5x)</t>
+  </si>
+  <si>
+    <t>AC to Superior (1.5x)</t>
+  </si>
+  <si>
+    <t>AC to Superior (0.5x)</t>
+  </si>
+  <si>
+    <t>AC to Port Wing (2x)</t>
   </si>
 </sst>
 </file>
@@ -15750,118 +15783,1026 @@
       </c>
     </row>
     <row r="372" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C372" s="8"/>
-      <c r="D372" s="9"/>
-      <c r="E372" s="9"/>
-      <c r="F372" s="10"/>
-      <c r="G372" s="10"/>
+      <c r="A372" s="33">
+        <v>45977</v>
+      </c>
+      <c r="B372" t="s">
+        <v>162</v>
+      </c>
+      <c r="C372" s="8">
+        <v>113052.5</v>
+      </c>
+      <c r="D372" s="9">
+        <v>15.496</v>
+      </c>
+      <c r="E372" s="9">
+        <v>2.5489999999999999</v>
+      </c>
+      <c r="F372" s="10">
+        <v>39.5</v>
+      </c>
+      <c r="G372" s="21">
+        <v>0</v>
+      </c>
+      <c r="H372" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I372" s="24">
+        <v>0</v>
+      </c>
+      <c r="K372" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L372" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="373" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C373" s="8"/>
-      <c r="D373" s="9"/>
-      <c r="E373" s="9"/>
-      <c r="F373" s="10"/>
-      <c r="G373" s="10"/>
+      <c r="A373" s="33">
+        <v>45986</v>
+      </c>
+      <c r="B373" t="s">
+        <v>27</v>
+      </c>
+      <c r="C373" s="8">
+        <v>113372.3</v>
+      </c>
+      <c r="D373" s="9">
+        <v>17.844999999999999</v>
+      </c>
+      <c r="E373" s="9">
+        <v>2.7490000000000001</v>
+      </c>
+      <c r="F373" s="10">
+        <v>49.06</v>
+      </c>
+      <c r="G373" s="21">
+        <v>0</v>
+      </c>
+      <c r="H373" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I373" s="24">
+        <v>0</v>
+      </c>
+      <c r="K373" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L373" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="374" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C374" s="8"/>
-      <c r="D374" s="9"/>
-      <c r="E374" s="9"/>
-      <c r="F374" s="10"/>
-      <c r="G374" s="10"/>
+      <c r="A374" s="33">
+        <v>45992</v>
+      </c>
+      <c r="B374" t="s">
+        <v>17</v>
+      </c>
+      <c r="C374" s="8">
+        <v>113626.3</v>
+      </c>
+      <c r="D374" s="9">
+        <v>14.737</v>
+      </c>
+      <c r="E374" s="9">
+        <v>2.7989999999999999</v>
+      </c>
+      <c r="F374" s="10">
+        <v>41.25</v>
+      </c>
+      <c r="G374" s="21">
+        <v>0</v>
+      </c>
+      <c r="H374" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I374" s="24">
+        <v>0</v>
+      </c>
+      <c r="J374" t="s">
+        <v>19</v>
+      </c>
+      <c r="K374" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L374" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="375" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C375" s="8"/>
-      <c r="D375" s="9"/>
-      <c r="E375" s="9"/>
-      <c r="F375" s="10"/>
-      <c r="G375" s="10"/>
+      <c r="A375" s="33">
+        <v>45997</v>
+      </c>
+      <c r="B375" t="s">
+        <v>73</v>
+      </c>
+      <c r="C375" s="8">
+        <v>113760.2</v>
+      </c>
+      <c r="D375" s="9">
+        <v>7.8540000000000001</v>
+      </c>
+      <c r="E375" s="9">
+        <v>2.419</v>
+      </c>
+      <c r="F375" s="10">
+        <v>19</v>
+      </c>
+      <c r="G375" s="21">
+        <v>0</v>
+      </c>
+      <c r="H375" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I375" s="24">
+        <v>0</v>
+      </c>
+      <c r="K375" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L375" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="376" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C376" s="8"/>
-      <c r="D376" s="9"/>
-      <c r="E376" s="9"/>
-      <c r="F376" s="10"/>
-      <c r="G376" s="10"/>
+      <c r="A376" s="33">
+        <v>46012</v>
+      </c>
+      <c r="B376" t="s">
+        <v>162</v>
+      </c>
+      <c r="C376" s="8">
+        <v>114077.7</v>
+      </c>
+      <c r="D376" s="9">
+        <v>18.361000000000001</v>
+      </c>
+      <c r="E376" s="9">
+        <v>2.3690000000000002</v>
+      </c>
+      <c r="F376" s="10">
+        <v>43.5</v>
+      </c>
+      <c r="G376" s="21">
+        <v>0</v>
+      </c>
+      <c r="H376" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I376" s="24">
+        <v>0</v>
+      </c>
+      <c r="K376" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L376" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="377" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C377" s="8"/>
-      <c r="D377" s="9"/>
-      <c r="E377" s="9"/>
-      <c r="F377" s="10"/>
-      <c r="G377" s="10"/>
+      <c r="A377" s="33">
+        <v>46015</v>
+      </c>
+      <c r="B377" t="s">
+        <v>86</v>
+      </c>
+      <c r="C377" s="8">
+        <v>114352</v>
+      </c>
+      <c r="D377" s="9">
+        <v>15.218</v>
+      </c>
+      <c r="E377" s="9">
+        <v>2.3490000000000002</v>
+      </c>
+      <c r="F377" s="10">
+        <v>35.75</v>
+      </c>
+      <c r="G377" s="21">
+        <v>0</v>
+      </c>
+      <c r="H377" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I377" s="24">
+        <v>0</v>
+      </c>
+      <c r="K377" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L377" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="378" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C378" s="8"/>
-      <c r="D378" s="9"/>
-      <c r="E378" s="9"/>
-      <c r="F378" s="10"/>
-      <c r="G378" s="10"/>
+      <c r="A378" s="33">
+        <v>46016</v>
+      </c>
+      <c r="B378" t="s">
+        <v>153</v>
+      </c>
+      <c r="C378" s="8">
+        <v>114603.6</v>
+      </c>
+      <c r="D378" s="9">
+        <v>11.569000000000001</v>
+      </c>
+      <c r="E378" s="9">
+        <v>2.399</v>
+      </c>
+      <c r="F378" s="10">
+        <v>27.75</v>
+      </c>
+      <c r="G378" s="21">
+        <v>0</v>
+      </c>
+      <c r="H378" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I378" s="24">
+        <v>0</v>
+      </c>
+      <c r="K378" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L378" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="379" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C379" s="8"/>
-      <c r="D379" s="9"/>
-      <c r="E379" s="9"/>
-      <c r="F379" s="10"/>
-      <c r="G379" s="10"/>
+      <c r="A379" s="33">
+        <v>46030</v>
+      </c>
+      <c r="B379" t="s">
+        <v>17</v>
+      </c>
+      <c r="C379" s="8">
+        <v>114936.6</v>
+      </c>
+      <c r="D379" s="9">
+        <v>19.207000000000001</v>
+      </c>
+      <c r="E379" s="9">
+        <v>2.4990000000000001</v>
+      </c>
+      <c r="F379" s="10">
+        <v>48</v>
+      </c>
+      <c r="G379" s="21">
+        <v>0</v>
+      </c>
+      <c r="H379" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I379" s="24">
+        <v>0</v>
+      </c>
+      <c r="K379" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L379" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="380" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C380" s="8"/>
-      <c r="D380" s="9"/>
-      <c r="E380" s="9"/>
-      <c r="F380" s="10"/>
-      <c r="G380" s="10"/>
+      <c r="A380" s="33">
+        <v>46057</v>
+      </c>
+      <c r="B380" t="s">
+        <v>17</v>
+      </c>
+      <c r="C380" s="8">
+        <v>115270.7</v>
+      </c>
+      <c r="D380" s="9">
+        <v>19.622</v>
+      </c>
+      <c r="E380" s="9">
+        <v>2.5990000000000002</v>
+      </c>
+      <c r="F380" s="10">
+        <v>51</v>
+      </c>
+      <c r="G380" s="21">
+        <v>0</v>
+      </c>
+      <c r="H380" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I380" s="24">
+        <v>0</v>
+      </c>
+      <c r="K380" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L380" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="381" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C381" s="8"/>
-      <c r="D381" s="9"/>
-      <c r="E381" s="9"/>
-      <c r="F381" s="10"/>
-      <c r="G381" s="10"/>
+      <c r="A381" s="33">
+        <v>46085</v>
+      </c>
+      <c r="B381" t="s">
+        <v>17</v>
+      </c>
+      <c r="C381" s="8">
+        <v>115512.8</v>
+      </c>
+      <c r="D381" s="9">
+        <v>14.925000000000001</v>
+      </c>
+      <c r="E381" s="9">
+        <v>3.1989999999999998</v>
+      </c>
+      <c r="F381" s="10">
+        <v>47.75</v>
+      </c>
+      <c r="G381" s="21">
+        <v>0</v>
+      </c>
+      <c r="H381" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I381" s="24">
+        <v>0</v>
+      </c>
+      <c r="K381" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L381" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="382" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C382" s="8"/>
-      <c r="D382" s="9"/>
-      <c r="E382" s="9"/>
-      <c r="F382" s="10"/>
-      <c r="G382" s="10"/>
+      <c r="A382" s="33">
+        <v>46095</v>
+      </c>
+      <c r="B382" t="s">
+        <v>17</v>
+      </c>
+      <c r="C382" s="8">
+        <v>115753.3</v>
+      </c>
+      <c r="D382" s="9">
+        <v>12.275</v>
+      </c>
+      <c r="E382" s="9">
+        <v>3.2989999999999999</v>
+      </c>
+      <c r="F382" s="10">
+        <v>48.5</v>
+      </c>
+      <c r="G382" s="21">
+        <v>0</v>
+      </c>
+      <c r="H382" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I382" s="24">
+        <v>0</v>
+      </c>
+      <c r="K382" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L382" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="383" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C383" s="8"/>
-      <c r="D383" s="9"/>
-      <c r="E383" s="9"/>
-      <c r="F383" s="10"/>
-      <c r="G383" s="10"/>
+      <c r="A383" s="33">
+        <v>46101</v>
+      </c>
+      <c r="B383" t="s">
+        <v>162</v>
+      </c>
+      <c r="C383" s="8">
+        <v>116008.3</v>
+      </c>
+      <c r="D383" s="9">
+        <v>12.942</v>
+      </c>
+      <c r="E383" s="9">
+        <v>3.149</v>
+      </c>
+      <c r="F383" s="10">
+        <v>40.75</v>
+      </c>
+      <c r="G383" s="21">
+        <v>0</v>
+      </c>
+      <c r="H383" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I383" s="24">
+        <v>0</v>
+      </c>
+      <c r="K383" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L383" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="384" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C384" s="8"/>
-      <c r="D384" s="9"/>
-      <c r="E384" s="9"/>
-      <c r="F384" s="10"/>
-      <c r="G384" s="10"/>
-    </row>
-    <row r="385" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C385" s="8"/>
-      <c r="D385" s="9"/>
-      <c r="E385" s="9"/>
-      <c r="F385" s="10"/>
-      <c r="G385" s="10"/>
-    </row>
-    <row r="386" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="A384" s="33">
+        <v>46104</v>
+      </c>
+      <c r="B384" t="s">
+        <v>163</v>
+      </c>
+      <c r="C384" s="8">
+        <v>116313.1</v>
+      </c>
+      <c r="D384" s="9">
+        <v>14.234</v>
+      </c>
+      <c r="E384" s="9">
+        <v>3.2490000000000001</v>
+      </c>
+      <c r="F384" s="10">
+        <v>46.25</v>
+      </c>
+      <c r="G384" s="21">
+        <v>0</v>
+      </c>
+      <c r="H384" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I384" s="24">
+        <v>0</v>
+      </c>
+      <c r="K384" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L384" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="385" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A385" s="33">
+        <v>46105</v>
+      </c>
+      <c r="B385" t="s">
+        <v>162</v>
+      </c>
+      <c r="C385" s="8">
+        <v>116564.9</v>
+      </c>
+      <c r="D385" s="9">
+        <v>10.887</v>
+      </c>
+      <c r="E385" s="9">
+        <v>3.2789999999999999</v>
+      </c>
+      <c r="F385" s="10">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="G385" s="21">
+        <v>0</v>
+      </c>
+      <c r="H385" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I385" s="24">
+        <v>0</v>
+      </c>
+      <c r="K385" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L385" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="386" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A386" s="33">
+        <v>46112</v>
+      </c>
+      <c r="B386" t="s">
+        <v>17</v>
+      </c>
+      <c r="C386" s="19">
+        <v>116890.9</v>
+      </c>
+      <c r="D386" s="17">
+        <v>16.646999999999998</v>
+      </c>
+      <c r="E386" s="17">
+        <v>3.4990000000000001</v>
+      </c>
+      <c r="F386" s="10">
+        <v>58.25</v>
+      </c>
+      <c r="G386" s="21">
+        <v>0</v>
+      </c>
+      <c r="H386" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I386" s="24">
+        <v>0</v>
+      </c>
+      <c r="K386" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L386" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="387" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A387" s="33">
+        <v>46134</v>
+      </c>
+      <c r="B387" t="s">
+        <v>164</v>
+      </c>
+      <c r="C387" s="19">
+        <v>117251.5</v>
+      </c>
+      <c r="D387" s="17">
+        <v>19.577000000000002</v>
+      </c>
+      <c r="E387" s="17">
+        <v>3.7290000000000001</v>
+      </c>
+      <c r="F387" s="18">
+        <v>73</v>
+      </c>
+      <c r="G387" s="21">
+        <v>0</v>
+      </c>
+      <c r="H387" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I387" s="24">
+        <v>0</v>
+      </c>
+      <c r="K387" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L387" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="388" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A388" s="33">
+        <v>46145</v>
+      </c>
+      <c r="B388" t="s">
+        <v>17</v>
+      </c>
+      <c r="C388" s="19">
+        <v>117601.4</v>
+      </c>
+      <c r="D388" s="17">
+        <v>20.422999999999998</v>
+      </c>
+      <c r="E388" s="17">
+        <v>4.1989999999999998</v>
+      </c>
+      <c r="F388" s="18">
+        <v>85.76</v>
+      </c>
+      <c r="G388" s="21">
+        <v>0</v>
+      </c>
+      <c r="H388" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I388" s="24">
+        <v>70</v>
+      </c>
+      <c r="K388" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L388" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M388" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="389" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A389" s="33">
+        <v>46153</v>
+      </c>
+      <c r="B389" t="s">
+        <v>73</v>
+      </c>
+      <c r="C389" s="19">
+        <v>117849.5</v>
+      </c>
+      <c r="D389" s="17">
+        <v>16.638000000000002</v>
+      </c>
+      <c r="E389" s="17">
+        <v>4.149</v>
+      </c>
+      <c r="F389" s="18">
+        <v>69.03</v>
+      </c>
+      <c r="G389" s="21">
+        <v>0</v>
+      </c>
+      <c r="H389" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I389" s="24">
+        <f>70+100</f>
+        <v>170</v>
+      </c>
+      <c r="K389" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L389" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M389" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="390" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A390" s="33">
+        <v>46157</v>
+      </c>
+      <c r="B390" t="s">
+        <v>92</v>
+      </c>
+      <c r="C390" s="19">
+        <v>118040.8</v>
+      </c>
+      <c r="D390" s="17">
+        <v>10.612</v>
+      </c>
+      <c r="E390" s="17">
+        <v>4.0990000000000002</v>
+      </c>
+      <c r="F390" s="18">
+        <v>43.5</v>
+      </c>
+      <c r="G390" s="21">
+        <v>0</v>
+      </c>
+      <c r="H390" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I390" s="24">
+        <v>100</v>
+      </c>
+      <c r="K390" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L390" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M390" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="391" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A391" s="33">
+        <v>46162</v>
+      </c>
+      <c r="B391" t="s">
+        <v>17</v>
+      </c>
+      <c r="C391" s="19">
+        <v>118266.4</v>
+      </c>
+      <c r="D391" s="17">
+        <v>13.638999999999999</v>
+      </c>
+      <c r="E391" s="17">
+        <v>4.399</v>
+      </c>
+      <c r="F391" s="18">
+        <v>60</v>
+      </c>
+      <c r="G391" s="21">
+        <v>0</v>
+      </c>
+      <c r="H391" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I391" s="24">
+        <v>100</v>
+      </c>
+      <c r="K391" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L391" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M391" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="392" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A392" s="33">
+        <v>46168</v>
+      </c>
+      <c r="B392" t="s">
+        <v>17</v>
+      </c>
+      <c r="C392" s="19">
+        <v>118549.8</v>
+      </c>
+      <c r="D392" s="17">
+        <v>20.004000000000001</v>
+      </c>
+      <c r="E392" s="17">
+        <v>4.399</v>
+      </c>
+      <c r="F392" s="18">
+        <v>88</v>
+      </c>
+      <c r="G392" s="21">
+        <v>0</v>
+      </c>
+      <c r="H392" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I392" s="24">
+        <v>200</v>
+      </c>
+      <c r="K392" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L392" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M392" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="393" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A393" s="33">
+        <v>46176</v>
+      </c>
+      <c r="B393" t="s">
+        <v>73</v>
+      </c>
+      <c r="C393" s="19">
+        <v>118823.3</v>
+      </c>
+      <c r="D393" s="17">
+        <v>17.111000000000001</v>
+      </c>
+      <c r="E393" s="17">
+        <v>4.0789999999999997</v>
+      </c>
+      <c r="F393" s="18">
+        <v>69.8</v>
+      </c>
+      <c r="G393" s="21">
+        <v>0</v>
+      </c>
+      <c r="H393" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I393" s="24">
+        <v>250</v>
+      </c>
+      <c r="K393" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L393" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M393" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="394" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A394" s="33">
+        <v>46183</v>
+      </c>
+      <c r="B394" t="s">
+        <v>73</v>
+      </c>
+      <c r="C394" s="19">
+        <v>119058.3</v>
+      </c>
+      <c r="D394" s="17">
+        <v>14.965</v>
+      </c>
+      <c r="E394" s="17">
+        <v>3.9590000000000001</v>
+      </c>
+      <c r="F394" s="18">
+        <v>59.25</v>
+      </c>
+      <c r="G394" s="21">
+        <v>0</v>
+      </c>
+      <c r="H394" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I394" s="24">
+        <v>100</v>
+      </c>
+      <c r="K394" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L394" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M394" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="395" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A395" s="33">
+        <v>46189</v>
+      </c>
+      <c r="B395" t="s">
+        <v>166</v>
+      </c>
+      <c r="C395" s="19">
+        <v>119295.5</v>
+      </c>
+      <c r="D395" s="17">
+        <v>16.783000000000001</v>
+      </c>
+      <c r="E395" s="17">
+        <v>3.7989999999999999</v>
+      </c>
+      <c r="F395" s="18">
+        <v>63.76</v>
+      </c>
+      <c r="G395" s="21">
+        <v>0</v>
+      </c>
+      <c r="H395" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I395" s="24">
+        <v>150</v>
+      </c>
+      <c r="K395" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L395" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M395" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="396" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A396" s="33">
+        <v>46196</v>
+      </c>
+      <c r="B396" t="s">
+        <v>17</v>
+      </c>
+      <c r="C396" s="19">
+        <v>119632.6</v>
+      </c>
+      <c r="D396" s="17">
+        <v>20.712</v>
+      </c>
+      <c r="E396" s="17">
+        <v>3.899</v>
+      </c>
+      <c r="F396" s="18">
+        <v>80.760000000000005</v>
+      </c>
+      <c r="G396" s="21">
+        <v>0</v>
+      </c>
+      <c r="H396" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I396" s="24">
+        <v>150</v>
+      </c>
+      <c r="K396" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L396" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M396" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="397" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A397" s="33">
+        <v>46198</v>
+      </c>
+      <c r="B397" t="s">
+        <v>17</v>
+      </c>
+      <c r="C397" s="19">
+        <v>119754.9</v>
+      </c>
+      <c r="D397" s="17">
+        <v>9.1460000000000008</v>
+      </c>
+      <c r="E397" s="17">
+        <v>3.7589999999999999</v>
+      </c>
+      <c r="F397" s="18">
+        <v>34.75</v>
+      </c>
+      <c r="G397" s="21">
+        <v>0</v>
+      </c>
+      <c r="H397" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I397" s="24">
+        <v>50</v>
+      </c>
+      <c r="K397" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L397" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M397" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="398" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A398" s="33">
+        <v>46203</v>
+      </c>
+      <c r="B398" t="s">
+        <v>92</v>
+      </c>
+      <c r="C398" s="19">
+        <v>119927.3</v>
+      </c>
+      <c r="D398" s="17">
+        <v>10.329000000000001</v>
+      </c>
+      <c r="E398" s="17">
+        <v>3.379</v>
+      </c>
+      <c r="F398" s="18">
+        <v>34.9</v>
+      </c>
+      <c r="G398" s="21">
+        <v>0</v>
+      </c>
+      <c r="H398" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I398" s="24">
+        <v>70</v>
+      </c>
+      <c r="K398" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L398" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M398" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="399" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A399" s="33">
+        <v>46212</v>
+      </c>
+      <c r="B399" t="s">
+        <v>92</v>
+      </c>
+      <c r="C399" s="19">
+        <v>120236.9</v>
+      </c>
+      <c r="D399" s="17">
+        <v>18.491</v>
+      </c>
+      <c r="E399" s="17">
+        <v>3.399</v>
+      </c>
+      <c r="F399" s="18">
+        <v>62.85</v>
+      </c>
+      <c r="G399" s="21">
+        <v>0</v>
+      </c>
+      <c r="H399" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I399" s="24">
+        <v>60</v>
+      </c>
+      <c r="K399" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L399" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M399" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="400" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/portfolio/posts/_data/TRUCK_RECORDS.xlsx
+++ b/portfolio/posts/_data/TRUCK_RECORDS.xlsx
@@ -16277,7 +16277,7 @@
     </row>
     <row r="386" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="33">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="B386" t="s">
         <v>17</v>
@@ -16347,7 +16347,7 @@
     </row>
     <row r="388" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="33">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B388" t="s">
         <v>17</v>
@@ -16576,7 +16576,7 @@
     </row>
     <row r="394" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="33">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B394" t="s">
         <v>73</v>
